--- a/მომსახურების ანაზღაურება ცელერისი.xlsx
+++ b/მომსახურების ანაზღაურება ცელერისი.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\nana\deliverer\დეკლარაცია\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kurts\OneDrive\სამუშაო დაფა\excelpdf\bank-summary\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EEA80EC-7F5F-4E2C-BE41-F4ECE09C5401}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27CAA14D-596F-4C92-ACA6-A98D5E051AE2}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12650" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="გადასატანი" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
     <sheet name="თანხები" sheetId="2" r:id="rId3"/>
     <sheet name="Sheet1" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="179021"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="97">
   <si>
     <t>8</t>
   </si>
@@ -731,13 +731,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G1048576"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="33.6640625" customWidth="1"/>
-    <col min="2" max="2" width="26.21875" style="5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="53.21875" customWidth="1"/>
-    <col min="6" max="6" width="14.33203125" customWidth="1"/>
+    <col min="1" max="1" width="33.6328125" customWidth="1"/>
+    <col min="2" max="2" width="26.1796875" style="5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.6328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="53.1796875" customWidth="1"/>
+    <col min="6" max="6" width="14.36328125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -764,81 +764,81 @@
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" t="s">
-        <v>32</v>
+      <c r="A2">
+        <v>62003016407</v>
       </c>
       <c r="B2" s="8" t="str">
         <f>INDEX(ინფო!B:B,MATCH(A2,ინფო!A:A,0))</f>
-        <v>დავითი</v>
+        <v>დავით</v>
       </c>
       <c r="C2" s="8" t="str">
         <f>INDEX(ინფო!C:C,MATCH(A2,ინფო!A:A,0))</f>
-        <v>საყვარელიძე</v>
+        <v>სვირავა</v>
       </c>
       <c r="D2" s="8" t="s">
         <v>0</v>
       </c>
       <c r="E2">
         <f>INDEX(თანხები!D:D,MATCH(A2,თანხები!A:A,0))</f>
-        <v>2874</v>
+        <v>3740.44</v>
       </c>
       <c r="F2" s="5" t="str">
         <f>INDEX(ინფო!D:D,MATCH(A2,ინფო!A:A,0))</f>
-        <v>თბილისი გუდამაყრის ქ. N 2 ბ. 102</v>
+        <v>თბილისი</v>
       </c>
       <c r="G2" s="4" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" t="s">
-        <v>24</v>
+      <c r="A3">
+        <v>47001040600</v>
       </c>
       <c r="B3" s="8" t="str">
         <f>INDEX(ინფო!B:B,MATCH(A3,ინფო!A:A,0))</f>
-        <v>გიორგი</v>
+        <v>რობერტ</v>
       </c>
       <c r="C3" s="8" t="str">
         <f>INDEX(ინფო!C:C,MATCH(A3,ინფო!A:A,0))</f>
-        <v>მელაძე</v>
+        <v>ელოიძე</v>
       </c>
       <c r="D3" s="8" t="s">
         <v>0</v>
       </c>
       <c r="E3">
         <f>INDEX(თანხები!D:D,MATCH(A3,თანხები!A:A,0))</f>
-        <v>2243</v>
+        <v>1368.47</v>
       </c>
       <c r="F3" s="5" t="str">
         <f>INDEX(ინფო!D:D,MATCH(A3,ინფო!A:A,0))</f>
-        <v>საქართველო, ქალაქი თბილისი, ნიკოლოზ ანთელავას ქუჩა, N 4(ყოფ. პ. იბერის ქ.)</v>
+        <v>თბილისი</v>
       </c>
       <c r="G3" s="4" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:7">
-      <c r="A4">
-        <v>62003016407</v>
+      <c r="A4" t="s">
+        <v>32</v>
       </c>
       <c r="B4" s="8" t="str">
         <f>INDEX(ინფო!B:B,MATCH(A4,ინფო!A:A,0))</f>
-        <v>დავით</v>
+        <v>დავითი</v>
       </c>
       <c r="C4" s="8" t="str">
         <f>INDEX(ინფო!C:C,MATCH(A4,ინფო!A:A,0))</f>
-        <v>სვირავა</v>
+        <v>საყვარელიძე</v>
       </c>
       <c r="D4" s="8" t="s">
         <v>0</v>
       </c>
       <c r="E4">
         <f>INDEX(თანხები!D:D,MATCH(A4,თანხები!A:A,0))</f>
-        <v>1438</v>
+        <v>1326</v>
       </c>
       <c r="F4" s="5" t="str">
         <f>INDEX(ინფო!D:D,MATCH(A4,ინფო!A:A,0))</f>
-        <v>თბილისი</v>
+        <v>თბილისი გუდამაყრის ქ. N 2 ბ. 102</v>
       </c>
       <c r="G4" s="4" t="s">
         <v>1</v>
@@ -846,50 +846,53 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="B5" s="8" t="str">
         <f>INDEX(ინფო!B:B,MATCH(A5,ინფო!A:A,0))</f>
-        <v>მიხეილ</v>
+        <v>გიორგი</v>
       </c>
       <c r="C5" s="8" t="str">
         <f>INDEX(ინფო!C:C,MATCH(A5,ინფო!A:A,0))</f>
-        <v>ლომჯარია</v>
+        <v>მელაძე</v>
       </c>
       <c r="D5" s="8" t="s">
         <v>0</v>
       </c>
       <c r="E5">
         <f>INDEX(თანხები!D:D,MATCH(A5,თანხები!A:A,0))</f>
-        <v>647</v>
+        <v>1267.17</v>
       </c>
       <c r="F5" s="5" t="str">
         <f>INDEX(ინფო!D:D,MATCH(A5,ინფო!A:A,0))</f>
-        <v>საქართველო, ქალაქი თბილისი, შალვა ნუცუბიძის ფერდობი, IV მიკრო/რაიონი, კორპუსი 12, ბინა 3</v>
+        <v>საქართველო, ქალაქი თბილისი, ნიკოლოზ ანთელავას ქუჩა, N 4(ყოფ. პ. იბერის ქ.)</v>
       </c>
       <c r="G5" s="4" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:7">
-      <c r="B6" s="8" t="e">
+      <c r="A6" t="s">
+        <v>64</v>
+      </c>
+      <c r="B6" s="8" t="str">
         <f>INDEX(ინფო!B:B,MATCH(A6,ინფო!A:A,0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="C6" s="8" t="e">
+        <v>ბადრი</v>
+      </c>
+      <c r="C6" s="8" t="str">
         <f>INDEX(ინფო!C:C,MATCH(A6,ინფო!A:A,0))</f>
-        <v>#N/A</v>
+        <v>სირაძე</v>
       </c>
       <c r="D6" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="E6" t="e">
+      <c r="E6">
         <f>INDEX(თანხები!D:D,MATCH(A6,თანხები!A:A,0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F6" s="5" t="e">
+        <v>1114</v>
+      </c>
+      <c r="F6" s="5" t="str">
         <f>INDEX(ინფო!D:D,MATCH(A6,ინფო!A:A,0))</f>
-        <v>#N/A</v>
+        <v>თბილისი გარდაბნის გზატ. N 42</v>
       </c>
       <c r="G6" s="4" t="s">
         <v>1</v>
@@ -1194,12 +1197,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{604AE93E-E511-4BD8-A9E1-AE041AC99209}">
   <dimension ref="A1:D26"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.21875" customWidth="1"/>
-    <col min="3" max="3" width="16.109375" customWidth="1"/>
-    <col min="4" max="4" width="87.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1796875" customWidth="1"/>
+    <col min="3" max="3" width="16.08984375" customWidth="1"/>
+    <col min="4" max="4" width="87.36328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
@@ -1575,12 +1578,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA7E4943-2DCB-430A-830C-82E1F3476269}">
   <dimension ref="A1:E26"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="21.21875" style="6" customWidth="1"/>
-    <col min="2" max="2" width="19.5546875" customWidth="1"/>
-    <col min="3" max="3" width="18.109375" customWidth="1"/>
-    <col min="4" max="4" width="9.109375" style="17" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="21.1796875" style="6" customWidth="1"/>
+    <col min="2" max="2" width="19.54296875" customWidth="1"/>
+    <col min="3" max="3" width="18.08984375" customWidth="1"/>
+    <col min="4" max="4" width="9.08984375" style="17" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1599,83 +1602,88 @@
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" t="str">
+      <c r="A2">
         <f>INDEX(ინფო!A:A,MATCH(C2,ინფო!C:C,0))</f>
-        <v>38001048993</v>
+        <v>62003016407</v>
       </c>
       <c r="B2" t="str">
         <f>INDEX(ინფო!B:B,MATCH(C2,ინფო!C:C,0))</f>
-        <v>დავითი</v>
+        <v>დავით</v>
       </c>
       <c r="C2" s="18" t="s">
-        <v>30</v>
+        <v>92</v>
       </c>
       <c r="D2" s="18">
-        <v>2874</v>
+        <v>3740.44</v>
       </c>
       <c r="E2" s="5"/>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" t="str">
+      <c r="A3">
         <f>INDEX(ინფო!A:A,MATCH(C3,ინფო!C:C,0))</f>
-        <v>01030053229</v>
+        <v>47001040600</v>
       </c>
       <c r="B3" t="str">
         <f>INDEX(ინფო!B:B,MATCH(C3,ინფო!C:C,0))</f>
-        <v>გიორგი</v>
+        <v>რობერტ</v>
       </c>
       <c r="C3" s="18" t="s">
-        <v>22</v>
+        <v>86</v>
       </c>
       <c r="D3" s="18">
-        <v>2243</v>
+        <v>1368.47</v>
       </c>
       <c r="E3" s="5"/>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4">
+      <c r="A4" t="str">
         <f>INDEX(ინფო!A:A,MATCH(C4,ინფო!C:C,0))</f>
-        <v>62003016407</v>
+        <v>38001048993</v>
       </c>
       <c r="B4" t="str">
         <f>INDEX(ინფო!B:B,MATCH(C4,ინფო!C:C,0))</f>
-        <v>დავით</v>
+        <v>დავითი</v>
       </c>
       <c r="C4" s="18" t="s">
-        <v>92</v>
+        <v>30</v>
       </c>
       <c r="D4" s="18">
-        <v>1438</v>
+        <v>1326</v>
       </c>
       <c r="E4" s="5"/>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" t="str">
         <f>INDEX(ინფო!A:A,MATCH(C5,ინფო!C:C,0))</f>
-        <v>01010000461</v>
+        <v>01030053229</v>
       </c>
       <c r="B5" t="str">
         <f>INDEX(ინფო!B:B,MATCH(C5,ინფო!C:C,0))</f>
-        <v>მიხეილ</v>
+        <v>გიორგი</v>
       </c>
       <c r="C5" s="18" t="s">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="D5" s="18">
-        <v>647</v>
+        <v>1267.17</v>
       </c>
       <c r="E5" s="5"/>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" t="e">
+      <c r="A6" t="str">
         <f>INDEX(ინფო!A:A,MATCH(C6,ინფო!C:C,0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="B6" t="e">
+        <v>22001020425</v>
+      </c>
+      <c r="B6" t="str">
         <f>INDEX(ინფო!B:B,MATCH(C6,ინფო!C:C,0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="D6" s="18"/>
+        <v>ბადრი</v>
+      </c>
+      <c r="C6" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="D6" s="18">
+        <v>1114</v>
+      </c>
       <c r="E6" s="5"/>
     </row>
     <row r="7" spans="1:5">
@@ -1837,71 +1845,80 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E21D28A8-2A04-4213-9FF0-5FC7E21D8E88}">
   <dimension ref="A2:M11"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="9.77734375" style="13" customWidth="1"/>
-    <col min="2" max="2" width="13.5546875" style="19" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="25.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.81640625" style="13" customWidth="1"/>
+    <col min="2" max="2" width="13.54296875" style="19" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="25.6328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:13">
       <c r="B2" s="18"/>
-      <c r="C2" s="18" t="s">
-        <v>30</v>
-      </c>
-      <c r="D2" s="18">
-        <v>2874</v>
-      </c>
+      <c r="C2" s="18"/>
+      <c r="D2" s="18"/>
     </row>
     <row r="3" spans="1:13">
       <c r="B3" s="18"/>
-      <c r="C3" s="18" t="s">
-        <v>22</v>
-      </c>
-      <c r="D3" s="18">
-        <v>2243</v>
-      </c>
+      <c r="C3" s="18"/>
+      <c r="D3" s="18"/>
     </row>
     <row r="4" spans="1:13">
       <c r="B4" s="18"/>
-      <c r="C4" s="18" t="s">
-        <v>92</v>
-      </c>
-      <c r="D4" s="18">
-        <v>1438</v>
-      </c>
+      <c r="C4" s="18"/>
+      <c r="D4" s="18"/>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="14"/>
-      <c r="C5" s="18" t="s">
-        <v>3</v>
-      </c>
-      <c r="D5" s="18">
-        <v>647</v>
-      </c>
+      <c r="C5" s="18"/>
+      <c r="D5" s="18"/>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="15"/>
-      <c r="C6" s="18"/>
+      <c r="C6" s="18" t="s">
+        <v>92</v>
+      </c>
+      <c r="D6" s="18">
+        <v>3740.44</v>
+      </c>
       <c r="M6" s="17"/>
     </row>
     <row r="7" spans="1:13">
-      <c r="C7" s="18"/>
+      <c r="C7" s="18" t="s">
+        <v>86</v>
+      </c>
+      <c r="D7" s="18">
+        <v>1368.47</v>
+      </c>
       <c r="M7" s="17"/>
     </row>
     <row r="8" spans="1:13">
       <c r="A8" s="15"/>
-      <c r="C8" s="18"/>
+      <c r="C8" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" s="18">
+        <v>1326</v>
+      </c>
       <c r="M8" s="17"/>
     </row>
     <row r="9" spans="1:13">
       <c r="A9" s="15"/>
-      <c r="C9" s="18"/>
+      <c r="C9" s="18" t="s">
+        <v>22</v>
+      </c>
+      <c r="D9" s="18">
+        <v>1267.17</v>
+      </c>
       <c r="M9" s="17"/>
     </row>
     <row r="10" spans="1:13">
       <c r="A10" s="15"/>
-      <c r="C10" s="18"/>
+      <c r="C10" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="D10" s="18">
+        <v>1114</v>
+      </c>
       <c r="M10" s="17"/>
     </row>
     <row r="11" spans="1:13">

--- a/მომსახურების ანაზღაურება ცელერისი.xlsx
+++ b/მომსახურების ანაზღაურება ცელერისი.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20417"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kurts\OneDrive\სამუშაო დაფა\excelpdf\bank-summary\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\nana\bank-summary\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27CAA14D-596F-4C92-ACA6-A98D5E051AE2}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B5F25BE-BB36-4336-A9D2-74423B39F50C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12650" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="გადასატანი" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
     <sheet name="თანხები" sheetId="2" r:id="rId3"/>
     <sheet name="Sheet1" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="179021"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -731,13 +731,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G1048576"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="33.6328125" customWidth="1"/>
-    <col min="2" max="2" width="26.1796875" style="5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.6328125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="53.1796875" customWidth="1"/>
-    <col min="6" max="6" width="14.36328125" customWidth="1"/>
+    <col min="1" max="1" width="33.6640625" customWidth="1"/>
+    <col min="2" max="2" width="26.21875" style="5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="53.21875" customWidth="1"/>
+    <col min="6" max="6" width="14.33203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -1197,12 +1197,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{604AE93E-E511-4BD8-A9E1-AE041AC99209}">
   <dimension ref="A1:D26"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.1796875" customWidth="1"/>
-    <col min="3" max="3" width="16.08984375" customWidth="1"/>
-    <col min="4" max="4" width="87.36328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.21875" customWidth="1"/>
+    <col min="3" max="3" width="16.109375" customWidth="1"/>
+    <col min="4" max="4" width="87.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
@@ -1578,12 +1578,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA7E4943-2DCB-430A-830C-82E1F3476269}">
   <dimension ref="A1:E26"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="21.1796875" style="6" customWidth="1"/>
-    <col min="2" max="2" width="19.54296875" customWidth="1"/>
-    <col min="3" max="3" width="18.08984375" customWidth="1"/>
-    <col min="4" max="4" width="9.08984375" style="17" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="21.21875" style="6" customWidth="1"/>
+    <col min="2" max="2" width="19.5546875" customWidth="1"/>
+    <col min="3" max="3" width="18.109375" customWidth="1"/>
+    <col min="4" max="4" width="9.109375" style="17" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1845,11 +1845,11 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E21D28A8-2A04-4213-9FF0-5FC7E21D8E88}">
   <dimension ref="A2:M11"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="9.81640625" style="13" customWidth="1"/>
-    <col min="2" max="2" width="13.54296875" style="19" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="25.6328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.77734375" style="13" customWidth="1"/>
+    <col min="2" max="2" width="13.5546875" style="19" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="25.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:13">
